--- a/Result/profitability/9918.xlsx
+++ b/Result/profitability/9918.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>0.41625</v>
+        <v>0.55</v>
       </c>
       <c r="N2" t="n">
-        <v>28.85875</v>
+        <v>29.6475</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.465</v>
+        <v>0.56875</v>
       </c>
       <c r="N3" t="n">
-        <v>30.1775</v>
+        <v>31.0275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4575</v>
+        <v>0.5475</v>
       </c>
       <c r="N4" t="n">
-        <v>29.53875</v>
+        <v>29.5575</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.38</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>27.49625</v>
+        <v>27.72875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0.43875</v>
+        <v>0.53625</v>
       </c>
       <c r="N6" t="n">
-        <v>27.3975</v>
+        <v>28.00875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="N7" t="n">
-        <v>26.7825</v>
+        <v>27.9925</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.415</v>
+        <v>0.49375</v>
       </c>
       <c r="N8" t="n">
-        <v>26.5425</v>
+        <v>26.87625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.28</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3412500000000001</v>
+        <v>0.34125</v>
       </c>
       <c r="N12" t="n">
         <v>22.38375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9918</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>535</v>
+      </c>
+      <c r="D75" t="n">
+        <v>356</v>
+      </c>
+      <c r="E75" t="n">
+        <v>179</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>96</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>149</v>
+      </c>
+      <c r="J75" t="n">
+        <v>245</v>
+      </c>
+      <c r="K75" t="n">
+        <v>224</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.365</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.669999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08685751463890701</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.859999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05895404120443737</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
